--- a/Sprint_Review_Protocol_5.xlsx
+++ b/Sprint_Review_Protocol_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florian\Desktop\itp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D57E884-E2E7-403A-9381-E3B5761E4236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBACFC57-973C-43C3-B442-C5596C99FB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{5C77D34F-34C3-4D2F-849C-09193AE86D67}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>Sprint Review Protocol</t>
   </si>
@@ -116,7 +116,13 @@
     <t>S5FT1</t>
   </si>
   <si>
-    <t>Crouch Spam Fix</t>
+    <t>Highlight Pickup Items</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Es gab Probleme mit dem vorhandenen System</t>
   </si>
   <si>
     <t>S5FT2</t>
@@ -125,13 +131,34 @@
     <t>Show Keycards in Pause Menu</t>
   </si>
   <si>
-    <t>x</t>
+    <t>Schwierigkeiten mit Photoshop</t>
   </si>
   <si>
     <t>S5FT3</t>
   </si>
   <si>
     <t>Remove Keycard Counter</t>
+  </si>
+  <si>
+    <t>Einfache Umsetzung</t>
+  </si>
+  <si>
+    <t>S5FT4</t>
+  </si>
+  <si>
+    <t>Fix Crouch Spam</t>
+  </si>
+  <si>
+    <t>Es konnte keine Lösung gefunden werden</t>
+  </si>
+  <si>
+    <t>S5FT5</t>
+  </si>
+  <si>
+    <t>Fix Sprint System</t>
+  </si>
+  <si>
+    <t>Leichte Implementation</t>
   </si>
   <si>
     <t>Liked</t>
@@ -472,6 +499,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -488,15 +524,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -834,28 +861,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9" ht="26.25">
       <c r="A3" s="12"/>
@@ -873,129 +900,129 @@
         <v>1</v>
       </c>
       <c r="B4" s="30"/>
-      <c r="C4" s="22">
+      <c r="C4" s="25">
         <v>4</v>
       </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="32"/>
-      <c r="C5" s="23">
+      <c r="C5" s="26">
         <v>46168</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="31" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="32"/>
-      <c r="C6" s="24">
+      <c r="C6" s="27">
         <v>35</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="32"/>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="31" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="32"/>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="32"/>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="31" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="32"/>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="31" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="32"/>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="33" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="34"/>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
@@ -1040,16 +1067,20 @@
         <f>D16-C16</f>
         <v>1</v>
       </c>
-      <c r="F16" s="13"/>
+      <c r="F16" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="G16" s="14"/>
-      <c r="H16" s="16"/>
+      <c r="H16" s="16" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="50.25" customHeight="1">
       <c r="A17" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17" s="15">
         <v>1</v>
@@ -1062,17 +1093,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14"/>
-      <c r="H17" s="16"/>
+      <c r="H17" s="16" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="50.25" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C18" s="15">
         <v>0.1</v>
@@ -1085,36 +1118,62 @@
         <v>0</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G18" s="14"/>
-      <c r="H18" s="16"/>
+      <c r="H18" s="16" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
+      <c r="A19" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="15">
+        <v>1</v>
+      </c>
+      <c r="D19" s="15">
+        <v>2</v>
+      </c>
       <c r="E19" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>D19-C19</f>
+        <v>1</v>
       </c>
       <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="16"/>
+      <c r="G19" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A20" s="15"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="A20" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>0.1</v>
+      </c>
       <c r="E20" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="13"/>
+        <f>D20-C20</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="G20" s="14"/>
-      <c r="H20" s="16"/>
+      <c r="H20" s="16" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="50.25" customHeight="1">
       <c r="A21" s="15"/>
@@ -1295,7 +1354,7 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3">
         <f>SUM(E16:E25)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="3">
         <f>COUNT(F16:F25)</f>
@@ -1310,16 +1369,16 @@
     <row r="36" spans="1:8" ht="24.75" customHeight="1">
       <c r="B36" s="4"/>
       <c r="C36" s="9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="60" customHeight="1">
@@ -1370,12 +1429,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
@@ -1390,6 +1443,12 @@
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="60" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/Sprint_Review_Protocol_5.xlsx
+++ b/Sprint_Review_Protocol_5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florian\Desktop\itp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBACFC57-973C-43C3-B442-C5596C99FB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB62F286-BBD4-421F-8F9C-AE57A0F1AE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{5C77D34F-34C3-4D2F-849C-09193AE86D67}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="103">
   <si>
     <t>Sprint Review Protocol</t>
   </si>
@@ -149,7 +149,7 @@
     <t>Fix Crouch Spam</t>
   </si>
   <si>
-    <t>Es konnte keine Lösung gefunden werden</t>
+    <t>Es konnte noch keine Lösung gefunden werden</t>
   </si>
   <si>
     <t>S5FT5</t>
@@ -161,6 +161,120 @@
     <t>Leichte Implementation</t>
   </si>
   <si>
+    <t>S3SH1</t>
+  </si>
+  <si>
+    <t>Aufzug +Schacht</t>
+  </si>
+  <si>
+    <t>Durch externe Referenzen war die Umsetzung leicht</t>
+  </si>
+  <si>
+    <t>S4SH5</t>
+  </si>
+  <si>
+    <t>Lüftungschächte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benutzerdefinierte Texturen erstellt und Materialien importiert </t>
+  </si>
+  <si>
+    <t>S5AD1</t>
+  </si>
+  <si>
+    <t>Anpassen Footsteps(Gegner/Spieler)</t>
+  </si>
+  <si>
+    <t>Einfache Bearbeitung</t>
+  </si>
+  <si>
+    <t>S5AD2</t>
+  </si>
+  <si>
+    <t>Anpassen Opening Door Sound</t>
+  </si>
+  <si>
+    <t>Weitere Sounds mussten implementiert werden und bisherige bearbeitet</t>
+  </si>
+  <si>
+    <t>S5AD3</t>
+  </si>
+  <si>
+    <t>Lampen Sounds flickern</t>
+  </si>
+  <si>
+    <t>Leichtere Lösung als gedacht</t>
+  </si>
+  <si>
+    <t>S5AD4</t>
+  </si>
+  <si>
+    <t>Keycard Sounds</t>
+  </si>
+  <si>
+    <t>Länger gedauert weil Bearbeitung</t>
+  </si>
+  <si>
+    <t>S5AD5</t>
+  </si>
+  <si>
+    <t>Erschöpfungssound</t>
+  </si>
+  <si>
+    <t>Noch nicht gemacht</t>
+  </si>
+  <si>
+    <t>S5AD6</t>
+  </si>
+  <si>
+    <t>Enemy Chase Musik</t>
+  </si>
+  <si>
+    <t>Nicht vollständig fertig</t>
+  </si>
+  <si>
+    <t>S5SM1</t>
+  </si>
+  <si>
+    <t>Neue Räume erstellt und mit Objekten befüllt</t>
+  </si>
+  <si>
+    <t>Basis existiert bereits, offene Arbeiten betreffen hauptsächlich kleine Details</t>
+  </si>
+  <si>
+    <t>S4MS1</t>
+  </si>
+  <si>
+    <t>Animationr/Rigging Pt3</t>
+  </si>
+  <si>
+    <t>Nicht umgesetzt da Zeit für Statetree Konvertierung verwendet wurde</t>
+  </si>
+  <si>
+    <t>S4MS2</t>
+  </si>
+  <si>
+    <t>Pathfinding/Collision</t>
+  </si>
+  <si>
+    <t>Neues NavMesh erstellt und Projectsettings abgeändert</t>
+  </si>
+  <si>
+    <t>S4MS3</t>
+  </si>
+  <si>
+    <t>Enemy open door logic</t>
+  </si>
+  <si>
+    <t>S4MS4</t>
+  </si>
+  <si>
+    <t>Enemy lose sight logic</t>
+  </si>
+  <si>
+    <t>Dank Hilfe von Fabian in Statetree Konvertiert</t>
+  </si>
+  <si>
     <t>Liked</t>
   </si>
   <si>
@@ -171,6 +285,66 @@
   </si>
   <si>
     <t>Longed for</t>
+  </si>
+  <si>
+    <t>Zusammenarbeit mit dem Team, verbessern vieler kleiner Audio-Details</t>
+  </si>
+  <si>
+    <t>Mehr Gefühl für Timing und Synchronisation von Sounds entwickelt</t>
+  </si>
+  <si>
+    <t>Teilweise noch Erfahrung bei komplexeren Audio-Systemen</t>
+  </si>
+  <si>
+    <t>Mehr Zeit um weitere Sounds und Chase-Musik fertigzustellen</t>
+  </si>
+  <si>
+    <t>Die Erstellung von benutzerdefinierten Modelle</t>
+  </si>
+  <si>
+    <t>Besserer Umgang mit Fusion360</t>
+  </si>
+  <si>
+    <t>Erfahrung mit Animationen</t>
+  </si>
+  <si>
+    <t>Mehr Zeit um die Beleuchtung im Level zu bearbeiten</t>
+  </si>
+  <si>
+    <t>Objekte manuell zu erstellen und selbstständig entscheiden zu können, wie etwas aussehen kann</t>
+  </si>
+  <si>
+    <t>Objekte selbst erstellen</t>
+  </si>
+  <si>
+    <t>Wissen, wie man kurvige Objekte erstellt und miteinander verbindet</t>
+  </si>
+  <si>
+    <t>Verständnis für Objektverbindungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erfolgserlebnis beim Testen durch bessere NavMesh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeiten mit Statetrees </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gute Documentation/Tutorials für Statetrees</t>
+  </si>
+  <si>
+    <t>Mehr Vorwissen über State Trees hätte mir geholfen, die Architektur früher richtig aufzubauen und spätere Umstrukturierungen zu vermeiden</t>
+  </si>
+  <si>
+    <t>Arbeiten mit StateTrees</t>
+  </si>
+  <si>
+    <t>Erfahrung im Bereich StateTrees</t>
+  </si>
+  <si>
+    <t>Erfahrung mit Post Process Materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mehr Zeit mit Bug-fixing </t>
   </si>
 </sst>
 </file>
@@ -499,6 +673,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -506,24 +698,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -861,28 +1035,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="26.25">
       <c r="A3" s="12"/>
@@ -900,129 +1074,129 @@
         <v>1</v>
       </c>
       <c r="B4" s="30"/>
-      <c r="C4" s="25">
-        <v>4</v>
-      </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="C4" s="22">
+        <v>5</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="32"/>
-      <c r="C5" s="26">
+      <c r="C5" s="23">
         <v>46168</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="31" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="32"/>
-      <c r="C6" s="27">
+      <c r="C6" s="24">
         <v>35</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="32"/>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="31" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="32"/>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="32"/>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="31" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="32"/>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="31" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="32"/>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="33" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="34"/>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
@@ -1176,173 +1350,328 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
+      <c r="A21" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="15">
+        <v>2</v>
+      </c>
+      <c r="D21" s="15">
+        <v>2</v>
+      </c>
       <c r="E21" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="13"/>
+      <c r="F21" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="G21" s="14"/>
-      <c r="H21" s="16"/>
+      <c r="H21" s="16" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
+      <c r="A22" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="15">
+        <v>3</v>
+      </c>
+      <c r="D22" s="15">
+        <v>3</v>
+      </c>
       <c r="E22" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="13"/>
+      <c r="F22" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="G22" s="14"/>
-      <c r="H22" s="16"/>
+      <c r="H22" s="16" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
+      <c r="A23" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
       <c r="E23" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="13"/>
+      <c r="F23" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="G23" s="14"/>
-      <c r="H23" s="16"/>
+      <c r="H23" s="16" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
+      <c r="A24" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="15">
+        <v>2</v>
+      </c>
+      <c r="D24" s="15">
+        <v>3</v>
+      </c>
       <c r="E24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="16"/>
+      <c r="H24" s="16" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
+      <c r="A25" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="15">
+        <v>2</v>
+      </c>
+      <c r="D25" s="15">
+        <v>0.5</v>
+      </c>
       <c r="E25" s="5">
         <f t="shared" si="0"/>
+        <v>-1.5</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="50.25" customHeight="1">
+      <c r="A26" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="15">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15">
+        <v>2</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="50.25" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="D27" s="15">
         <v>0</v>
       </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="16"/>
-    </row>
-    <row r="26" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="16"/>
-    </row>
-    <row r="27" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
       <c r="E27" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F27" s="13"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="16"/>
+      <c r="G27" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
+      <c r="A28" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="15">
+        <v>3</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
       <c r="E28" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F28" s="13"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="16"/>
+      <c r="G28" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
+      <c r="A29" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="15">
+        <v>9</v>
+      </c>
+      <c r="D29" s="15">
+        <v>19</v>
+      </c>
       <c r="E29" s="5">
         <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="50.25" customHeight="1">
+      <c r="A30" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="15">
         <v>0</v>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="16"/>
-    </row>
-    <row r="30" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
       <c r="E30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="13"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="16"/>
+      <c r="G30" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
+      <c r="A31" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="15">
+        <v>2</v>
+      </c>
+      <c r="D31" s="15">
+        <v>6</v>
+      </c>
       <c r="E31" s="5">
         <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="14"/>
+      <c r="H31" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="50.25" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="15">
+        <v>1</v>
+      </c>
+      <c r="D32" s="15">
         <v>0</v>
       </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="16"/>
-    </row>
-    <row r="32" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
       <c r="E32" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F32" s="13"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="16"/>
+      <c r="G32" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
+      <c r="A33" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="D33" s="15">
+        <v>6</v>
+      </c>
       <c r="E33" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="13"/>
+        <v>4.5</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="G33" s="14"/>
-      <c r="H33" s="16"/>
+      <c r="H33" s="16" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="3">
@@ -1354,7 +1683,7 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3">
         <f>SUM(E16:E25)</f>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F34" s="3">
         <f>COUNT(F16:F25)</f>
@@ -1369,66 +1698,112 @@
     <row r="36" spans="1:8" ht="24.75" customHeight="1">
       <c r="B36" s="4"/>
       <c r="C36" s="9" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="60" customHeight="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="69.75" customHeight="1">
       <c r="B37" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
+      <c r="C37" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="38" spans="1:8" ht="53.25" customHeight="1">
       <c r="A38"/>
       <c r="B38" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="18"/>
+      <c r="C38" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="96" customHeight="1">
       <c r="B39" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="18"/>
-    </row>
-    <row r="40" spans="1:8" ht="90.75" customHeight="1">
+      <c r="C39" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="133.5" customHeight="1">
       <c r="B40" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="19"/>
+      <c r="C40" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="41" spans="1:8" ht="60" customHeight="1">
       <c r="B41" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="11"/>
+      <c r="C41" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>102</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
@@ -1443,12 +1818,6 @@
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="60" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
